--- a/resources/templates/system/container_invoice_packing.xlsx
+++ b/resources/templates/system/container_invoice_packing.xlsx
@@ -13,7 +13,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'INVOICE'!$20:$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INVOICE'!$A$1:$L$121</definedName>
   </definedNames>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -45,14 +45,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">SSANCAR LTD.,
+    <t>SSANCAR LTD.,
 163 Sangidaehak-ro, Siheung-si,
 Gyeonggi-do, Republic of Korea
 TEL:82-505-355-9977 
 FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-    </r>
+EMAIL : ssancar9977@gmail.com</t>
   </si>
   <si>
     <r>
@@ -470,37 +468,37 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve"> SUB TOTAL :</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OCEAN FREIGHT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> GRAND TOTAL :</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Signed By    </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GASOLIN</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">LPG</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">GASOLIN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Signed By    </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> GRAND TOTAL :</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">OCEAN FREIGHT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> SUB TOTAL :</t>
     </r>
   </si>
 </sst>
@@ -2048,23 +2046,14 @@
       <c r="W2" s="83"/>
     </row>
     <row r="3" spans="1:23" customHeight="1" ht="15.75" s="83" customFormat="1">
-      <c r="B3" s="91" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">SSANCAR LTD.,
-163 Sangidaehak-ro, Siheung-si,
-Gyeonggi-do, Republic of Korea
-TEL:82-505-355-9977 
-FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
-          </r>
-        </is>
+      <c r="B3" s="91" t="s">
+        <v>5</v>
       </c>
       <c r="F3" s="92"/>
       <c r="G3" s="53"/>
-      <c r="J3" s="54">
+      <c r="J3" s="54" t="str">
         <f>TODAY()</f>
-        <v>46166</v>
+        <v>0</v>
       </c>
       <c r="L3" s="92"/>
       <c r="N3" s="77" t="inlineStr">
@@ -2909,9 +2898,9 @@
       <c r="H21" s="109">
         <v>2300</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="44" t="str">
         <f>H21</f>
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="J21" s="110">
         <v>1545</v>
@@ -2920,9 +2909,9 @@
       <c r="L21" s="112">
         <v>1075</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="14" t="str">
         <f>SUM(I21,L21)</f>
-        <v>3375</v>
+        <v>0</v>
       </c>
       <c r="N21" s="31" t="inlineStr">
         <is>
@@ -3114,9 +3103,9 @@
       <c r="H24" s="109">
         <v>6400</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="44" t="str">
         <f>H24</f>
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="J24" s="110">
         <v>3075</v>
@@ -3125,9 +3114,9 @@
       <c r="L24" s="112">
         <v>1075</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M24" s="14" t="str">
         <f>SUM(I24,L24)</f>
-        <v>7475</v>
+        <v>0</v>
       </c>
       <c r="N24" s="31" t="inlineStr">
         <is>
@@ -3312,9 +3301,9 @@
       <c r="H27" s="109">
         <v>5100</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="44" t="str">
         <f>H27</f>
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="110">
         <v>2965</v>
@@ -3323,9 +3312,9 @@
       <c r="L27" s="112">
         <v>1075</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M27" s="14" t="str">
         <f>SUM(I27,L27)</f>
-        <v>6175</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="7"/>
@@ -3435,9 +3424,9 @@
       <c r="H30" s="109">
         <v>1600</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="44" t="str">
         <f>H30</f>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="J30" s="110">
         <v>1535</v>
@@ -3446,9 +3435,9 @@
       <c r="L30" s="112">
         <v>1075</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="14" t="str">
         <f>SUM(I30,L30)</f>
-        <v>2675</v>
+        <v>0</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="7"/>
@@ -3538,14 +3527,14 @@
       <c r="F33" s="34"/>
       <c r="G33" s="10"/>
       <c r="H33" s="121"/>
-      <c r="I33" s="37">
+      <c r="I33" s="37" t="str">
         <f>H33</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J33" s="122"/>
       <c r="K33" s="123"/>
       <c r="L33" s="124"/>
-      <c r="M33" s="14">
+      <c r="M33" s="14" t="str">
         <f>SUM(I33,L33)</f>
         <v>0</v>
       </c>
@@ -3630,14 +3619,14 @@
       <c r="F36" s="34"/>
       <c r="G36" s="10"/>
       <c r="H36" s="121"/>
-      <c r="I36" s="37">
+      <c r="I36" s="37" t="str">
         <f>H36</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J36" s="122"/>
       <c r="K36" s="123"/>
       <c r="L36" s="124"/>
-      <c r="M36" s="14">
+      <c r="M36" s="14" t="str">
         <f>SUM(I36,L36)</f>
         <v>0</v>
       </c>
@@ -3722,14 +3711,14 @@
       <c r="F39" s="34"/>
       <c r="G39" s="10"/>
       <c r="H39" s="121"/>
-      <c r="I39" s="37">
+      <c r="I39" s="37" t="str">
         <f>H39</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J39" s="122"/>
       <c r="K39" s="123"/>
       <c r="L39" s="124"/>
-      <c r="M39" s="14">
+      <c r="M39" s="14" t="str">
         <f>SUM(I39,L39)</f>
         <v>0</v>
       </c>
@@ -3814,14 +3803,14 @@
       <c r="F42" s="34"/>
       <c r="G42" s="10"/>
       <c r="H42" s="121"/>
-      <c r="I42" s="37">
+      <c r="I42" s="37" t="str">
         <f>H42</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J42" s="122"/>
       <c r="K42" s="123"/>
       <c r="L42" s="124"/>
-      <c r="M42" s="14">
+      <c r="M42" s="14" t="str">
         <f>SUM(I42,L42)</f>
         <v>0</v>
       </c>
@@ -3906,14 +3895,14 @@
       <c r="F45" s="34"/>
       <c r="G45" s="10"/>
       <c r="H45" s="121"/>
-      <c r="I45" s="37">
+      <c r="I45" s="37" t="str">
         <f>H45</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J45" s="122"/>
       <c r="K45" s="123"/>
       <c r="L45" s="124"/>
-      <c r="M45" s="14">
+      <c r="M45" s="14" t="str">
         <f>SUM(I45,L45)</f>
         <v>0</v>
       </c>
@@ -3998,14 +3987,14 @@
       <c r="F48" s="34"/>
       <c r="G48" s="10"/>
       <c r="H48" s="121"/>
-      <c r="I48" s="37">
+      <c r="I48" s="37" t="str">
         <f>H48</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J48" s="122"/>
       <c r="K48" s="123"/>
       <c r="L48" s="124"/>
-      <c r="M48" s="14">
+      <c r="M48" s="14" t="str">
         <f>SUM(I48,L48)</f>
         <v>0</v>
       </c>
@@ -4090,14 +4079,14 @@
       <c r="F51" s="34"/>
       <c r="G51" s="10"/>
       <c r="H51" s="121"/>
-      <c r="I51" s="37">
+      <c r="I51" s="37" t="str">
         <f>H51</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J51" s="122"/>
       <c r="K51" s="123"/>
       <c r="L51" s="124"/>
-      <c r="M51" s="14">
+      <c r="M51" s="14" t="str">
         <f>SUM(I51,L51)</f>
         <v>0</v>
       </c>
@@ -4182,14 +4171,14 @@
       <c r="F54" s="34"/>
       <c r="G54" s="10"/>
       <c r="H54" s="121"/>
-      <c r="I54" s="37">
+      <c r="I54" s="37" t="str">
         <f>H54</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J54" s="122"/>
       <c r="K54" s="123"/>
       <c r="L54" s="124"/>
-      <c r="M54" s="14">
+      <c r="M54" s="14" t="str">
         <f>SUM(I54,L54)</f>
         <v>0</v>
       </c>
@@ -4274,14 +4263,14 @@
       <c r="F57" s="34"/>
       <c r="G57" s="10"/>
       <c r="H57" s="121"/>
-      <c r="I57" s="37">
+      <c r="I57" s="37" t="str">
         <f>H57</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J57" s="122"/>
       <c r="K57" s="123"/>
       <c r="L57" s="124"/>
-      <c r="M57" s="14">
+      <c r="M57" s="14" t="str">
         <f>SUM(I57,L57)</f>
         <v>0</v>
       </c>
@@ -4366,14 +4355,14 @@
       <c r="F60" s="34"/>
       <c r="G60" s="10"/>
       <c r="H60" s="121"/>
-      <c r="I60" s="37">
+      <c r="I60" s="37" t="str">
         <f>H60</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J60" s="122"/>
       <c r="K60" s="123"/>
       <c r="L60" s="124"/>
-      <c r="M60" s="14">
+      <c r="M60" s="14" t="str">
         <f>SUM(I60,L60)</f>
         <v>0</v>
       </c>
@@ -4458,14 +4447,14 @@
       <c r="F63" s="34"/>
       <c r="G63" s="10"/>
       <c r="H63" s="121"/>
-      <c r="I63" s="37">
+      <c r="I63" s="37" t="str">
         <f>H63</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J63" s="122"/>
       <c r="K63" s="123"/>
       <c r="L63" s="124"/>
-      <c r="M63" s="14">
+      <c r="M63" s="14" t="str">
         <f>SUM(I63,L63)</f>
         <v>0</v>
       </c>
@@ -4550,14 +4539,14 @@
       <c r="F66" s="34"/>
       <c r="G66" s="10"/>
       <c r="H66" s="121"/>
-      <c r="I66" s="37">
+      <c r="I66" s="37" t="str">
         <f>H66</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J66" s="122"/>
       <c r="K66" s="123"/>
       <c r="L66" s="124"/>
-      <c r="M66" s="14">
+      <c r="M66" s="14" t="str">
         <f>SUM(I66,L66)</f>
         <v>0</v>
       </c>
@@ -4642,14 +4631,14 @@
       <c r="F69" s="34"/>
       <c r="G69" s="10"/>
       <c r="H69" s="121"/>
-      <c r="I69" s="37">
+      <c r="I69" s="37" t="str">
         <f>H69</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J69" s="122"/>
       <c r="K69" s="123"/>
       <c r="L69" s="124"/>
-      <c r="M69" s="14">
+      <c r="M69" s="14" t="str">
         <f>SUM(I69,L69)</f>
         <v>0</v>
       </c>
@@ -4734,14 +4723,14 @@
       <c r="F72" s="34"/>
       <c r="G72" s="10"/>
       <c r="H72" s="121"/>
-      <c r="I72" s="37">
+      <c r="I72" s="37" t="str">
         <f>H72</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J72" s="122"/>
       <c r="K72" s="123"/>
       <c r="L72" s="124"/>
-      <c r="M72" s="14">
+      <c r="M72" s="14" t="str">
         <f>SUM(I72,L72)</f>
         <v>0</v>
       </c>
@@ -4826,14 +4815,14 @@
       <c r="F75" s="34"/>
       <c r="G75" s="10"/>
       <c r="H75" s="121"/>
-      <c r="I75" s="37">
+      <c r="I75" s="37" t="str">
         <f>H75</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J75" s="122"/>
       <c r="K75" s="123"/>
       <c r="L75" s="124"/>
-      <c r="M75" s="14">
+      <c r="M75" s="14" t="str">
         <f>SUM(I75,L75)</f>
         <v>0</v>
       </c>
@@ -4918,14 +4907,14 @@
       <c r="F78" s="34"/>
       <c r="G78" s="10"/>
       <c r="H78" s="121"/>
-      <c r="I78" s="37">
+      <c r="I78" s="37" t="str">
         <f>H78</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J78" s="122"/>
       <c r="K78" s="123"/>
       <c r="L78" s="124"/>
-      <c r="M78" s="14">
+      <c r="M78" s="14" t="str">
         <f>SUM(I78,L78)</f>
         <v>0</v>
       </c>
@@ -5010,14 +4999,14 @@
       <c r="F81" s="34"/>
       <c r="G81" s="10"/>
       <c r="H81" s="121"/>
-      <c r="I81" s="37">
+      <c r="I81" s="37" t="str">
         <f>H81</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J81" s="122"/>
       <c r="K81" s="123"/>
       <c r="L81" s="124"/>
-      <c r="M81" s="14">
+      <c r="M81" s="14" t="str">
         <f>SUM(I81,L81)</f>
         <v>0</v>
       </c>
@@ -5102,14 +5091,14 @@
       <c r="F84" s="34"/>
       <c r="G84" s="10"/>
       <c r="H84" s="121"/>
-      <c r="I84" s="37">
+      <c r="I84" s="37" t="str">
         <f>H84</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J84" s="122"/>
       <c r="K84" s="123"/>
       <c r="L84" s="124"/>
-      <c r="M84" s="14">
+      <c r="M84" s="14" t="str">
         <f>SUM(I84,L84)</f>
         <v>0</v>
       </c>
@@ -5194,14 +5183,14 @@
       <c r="F87" s="34"/>
       <c r="G87" s="10"/>
       <c r="H87" s="121"/>
-      <c r="I87" s="37">
+      <c r="I87" s="37" t="str">
         <f>H87</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J87" s="122"/>
       <c r="K87" s="123"/>
       <c r="L87" s="124"/>
-      <c r="M87" s="14">
+      <c r="M87" s="14" t="str">
         <f>SUM(I87,L87)</f>
         <v>0</v>
       </c>
@@ -5286,14 +5275,14 @@
       <c r="F90" s="34"/>
       <c r="G90" s="10"/>
       <c r="H90" s="121"/>
-      <c r="I90" s="37">
+      <c r="I90" s="37" t="str">
         <f>H90</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J90" s="122"/>
       <c r="K90" s="123"/>
       <c r="L90" s="124"/>
-      <c r="M90" s="14">
+      <c r="M90" s="14" t="str">
         <f>SUM(I90,L90)</f>
         <v>0</v>
       </c>
@@ -5378,14 +5367,14 @@
       <c r="F93" s="34"/>
       <c r="G93" s="10"/>
       <c r="H93" s="121"/>
-      <c r="I93" s="37">
+      <c r="I93" s="37" t="str">
         <f>H93</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J93" s="122"/>
       <c r="K93" s="123"/>
       <c r="L93" s="124"/>
-      <c r="M93" s="14">
+      <c r="M93" s="14" t="str">
         <f>SUM(I93,L93)</f>
         <v>0</v>
       </c>
@@ -5470,14 +5459,14 @@
       <c r="F96" s="34"/>
       <c r="G96" s="10"/>
       <c r="H96" s="121"/>
-      <c r="I96" s="37">
+      <c r="I96" s="37" t="str">
         <f>H96</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J96" s="122"/>
       <c r="K96" s="123"/>
       <c r="L96" s="124"/>
-      <c r="M96" s="14">
+      <c r="M96" s="14" t="str">
         <f>SUM(I96,L96)</f>
         <v>0</v>
       </c>
@@ -5562,14 +5551,14 @@
       <c r="F99" s="34"/>
       <c r="G99" s="10"/>
       <c r="H99" s="121"/>
-      <c r="I99" s="37">
+      <c r="I99" s="37" t="str">
         <f>H99</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J99" s="122"/>
       <c r="K99" s="123"/>
       <c r="L99" s="124"/>
-      <c r="M99" s="14">
+      <c r="M99" s="14" t="str">
         <f>SUM(I99,L99)</f>
         <v>0</v>
       </c>
@@ -5654,14 +5643,14 @@
       <c r="F102" s="34"/>
       <c r="G102" s="10"/>
       <c r="H102" s="121"/>
-      <c r="I102" s="37">
+      <c r="I102" s="37" t="str">
         <f>H102</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J102" s="122"/>
       <c r="K102" s="123"/>
       <c r="L102" s="124"/>
-      <c r="M102" s="14">
+      <c r="M102" s="14" t="str">
         <f>SUM(I102,L102)</f>
         <v>0</v>
       </c>
@@ -5746,14 +5735,14 @@
       <c r="F105" s="34"/>
       <c r="G105" s="10"/>
       <c r="H105" s="121"/>
-      <c r="I105" s="37">
+      <c r="I105" s="37" t="str">
         <f>H105</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J105" s="122"/>
       <c r="K105" s="123"/>
       <c r="L105" s="124"/>
-      <c r="M105" s="14">
+      <c r="M105" s="14" t="str">
         <f>SUM(I105,L105)</f>
         <v>0</v>
       </c>
@@ -5838,14 +5827,14 @@
       <c r="F108" s="34"/>
       <c r="G108" s="10"/>
       <c r="H108" s="121"/>
-      <c r="I108" s="37">
+      <c r="I108" s="37" t="str">
         <f>H108</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J108" s="122"/>
       <c r="K108" s="123"/>
       <c r="L108" s="124"/>
-      <c r="M108" s="14">
+      <c r="M108" s="14" t="str">
         <f>SUM(I108,L108)</f>
         <v>0</v>
       </c>
@@ -5939,21 +5928,21 @@
       </c>
       <c r="G111" s="85"/>
       <c r="H111" s="126"/>
-      <c r="I111" s="41">
+      <c r="I111" s="41" t="str">
         <f>SUM(I21:I110)</f>
-        <v>15400</v>
-      </c>
-      <c r="J111" s="43">
+        <v>0</v>
+      </c>
+      <c r="J111" s="43" t="str">
         <f>SUM(J21:J110)</f>
-        <v>9120</v>
-      </c>
-      <c r="K111" s="42">
+        <v>0</v>
+      </c>
+      <c r="K111" s="42" t="str">
         <f>SUM(K21:K110)</f>
         <v>0</v>
       </c>
-      <c r="L111" s="38">
+      <c r="L111" s="38" t="str">
         <f>SUM(L21:L110)</f>
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="M111" s="6"/>
       <c r="O111" s="7"/>
@@ -5992,9 +5981,9 @@
           </r>
         </is>
       </c>
-      <c r="I112" s="40">
+      <c r="I112" s="40" t="str">
         <f>SUM(L111)</f>
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="J112" s="130"/>
       <c r="K112" s="129"/>
@@ -6065,9 +6054,9 @@
       </c>
       <c r="G114" s="134"/>
       <c r="H114" s="9"/>
-      <c r="I114" s="39">
+      <c r="I114" s="39" t="str">
         <f>SUM(I111:I113)</f>
-        <v>19700</v>
+        <v>0</v>
       </c>
       <c r="J114" s="136"/>
       <c r="K114" s="135"/>
